--- a/DesignData/Portal.xlsx
+++ b/DesignData/Portal.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -458,47 +458,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>SrcX</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>SrcY</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>SrcZ</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
           <t>DestAreaId</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>DestX</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>DestY</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>DestZ</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>DestYaw</t>
         </is>
       </c>
     </row>
@@ -520,47 +480,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
           <t>ref:Area</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
         </is>
       </c>
     </row>
@@ -582,47 +502,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>server</t>
+          <t>both</t>
         </is>
       </c>
     </row>
@@ -644,47 +524,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>포털 위치의 X 좌표</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>포털 위치의 Y 좌표</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>포털 위치의 Z 좌표</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>포털을 탈 수 있는 평면 거리. 0보다 크다</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
           <t>도착 지역</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>도착 위치의 X 좌표</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>도착 위치의 Y 좌표</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>도착 위치의 Z 좌표</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>도착한 뒤의 방향(도)</t>
         </is>
       </c>
     </row>
@@ -701,31 +541,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1200</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>500</v>
-      </c>
-      <c r="H5" t="n">
         <v>20</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-8000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>180</v>
       </c>
     </row>
     <row r="6">
@@ -741,31 +557,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1200</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>500</v>
-      </c>
-      <c r="H6" t="n">
         <v>30</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-8000</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>180</v>
       </c>
     </row>
     <row r="7">
@@ -781,31 +573,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1200</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>500</v>
-      </c>
-      <c r="H7" t="n">
         <v>40</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-8000</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-10000</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>180</v>
       </c>
     </row>
     <row r="8">
@@ -821,31 +589,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-7750</v>
-      </c>
-      <c r="E8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>500</v>
-      </c>
-      <c r="H8" t="n">
         <v>10</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -861,31 +605,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-7750</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>500</v>
-      </c>
-      <c r="H9" t="n">
         <v>10</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -901,31 +621,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-7750</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-10000</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>500</v>
-      </c>
-      <c r="H10" t="n">
         <v>10</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
